--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-04T21:26:03Z</t>
+          <t>2026-06-06T19:27:08Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-06T19:27:08Z</t>
+          <t>2026-06-07T19:38:57Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-07T19:38:57Z</t>
+          <t>2026-06-07T20:20:56Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-07T20:20:56Z</t>
+          <t>2026-06-07T20:51:59Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-07T20:51:59Z</t>
+          <t>2026-06-07T21:51:44Z</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>varchar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>varchar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>varchar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>varchar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>varchar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>varchar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-07T21:51:44Z</t>
+          <t>2026-06-07T22:18:08Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-07T22:18:08Z</t>
+          <t>2026-06-07T22:58:48Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-07T22:58:48Z</t>
+          <t>2026-06-09T22:33:29Z</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-09T22:33:29Z</t>
+          <t>2026-06-10T22:12:58Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-10T22:12:58Z</t>
+          <t>2026-06-11T17:34:06Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-11T17:34:06Z</t>
+          <t>2026-06-11T19:18:19Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-11T19:18:19Z</t>
+          <t>2026-06-13T19:58:45Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-13T19:58:45Z</t>
+          <t>2026-06-14T12:51:54Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-14T12:51:54Z</t>
+          <t>2026-06-14T14:50:29Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-14T14:50:29Z</t>
+          <t>2026-06-14T15:57:09Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-14T15:57:09Z</t>
+          <t>2026-06-14T19:16:25Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-14T19:16:25Z</t>
+          <t>2026-06-14T22:28:53Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-14T22:28:53Z</t>
+          <t>2026-06-15T11:07:41Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-15T11:07:41Z</t>
+          <t>2026-06-15T13:17:51Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-15T13:17:51Z</t>
+          <t>2026-06-15T19:50:34Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -8,12 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CALENDAR" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PROJECT" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ipn_calendar" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ipn_project" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CALENDAR'!$A$1:$J$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PROJECT'!$A$1:$J$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ipn_calendar'!$A$1:$J$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ipn_project'!$A$1:$J$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-15T19:50:34Z</t>
+          <t>2026-06-27T19:29:17Z</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
@@ -623,7 +623,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>columnX1</t>
+          <t>columnx1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>columnX2</t>
+          <t>columnx2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>columnX3</t>
+          <t>columnx3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -697,7 +697,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>columnX4</t>
+          <t>columnx4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -744,7 +744,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>PROJECT.proj_id</t>
+          <t>ipn_project.proj_id</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
@@ -774,7 +774,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PROJECT.column1</t>
+          <t>ipn_project.column1</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr"/>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-27T19:29:17Z</t>
+          <t>2026-06-27T23:13:26Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-27T23:13:26Z</t>
+          <t>2026-06-28T12:29:41Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-28T12:29:41Z</t>
+          <t>2026-06-28T21:30:55Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-28T21:30:55Z</t>
+          <t>2026-06-28T22:23:06Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-28T22:23:06Z</t>
+          <t>2026-06-28T22:27:02Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-28T22:27:02Z</t>
+          <t>2026-06-29T22:01:15Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-29T22:01:15Z</t>
+          <t>2026-06-30T19:54:32Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-30T19:54:32Z</t>
+          <t>2026-06-30T23:30:24Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-30T23:30:24Z</t>
+          <t>2026-07-21T12:06:22Z</t>
         </is>
       </c>
     </row>

--- a/epics/1118/docs/data_dictionary.xlsx
+++ b/epics/1118/docs/data_dictionary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-21T12:06:22Z</t>
+          <t>2026-07-21T12:42:34Z</t>
         </is>
       </c>
     </row>
